--- a/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0001T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0001T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>102.5092965212124</v>
+        <v>16.65776068469701</v>
       </c>
       <c r="D2" t="n">
-        <v>14.80022429667282</v>
+        <v>2.405036448209334</v>
       </c>
       <c r="E2" t="n">
-        <v>10.5388278281932</v>
+        <v>1.712559522081396</v>
       </c>
       <c r="F2" t="n">
-        <v>24.94609779058719</v>
+        <v>4.053740890970418</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>94.85489397884116</v>
+        <v>15.41392027156169</v>
       </c>
       <c r="D3" t="n">
-        <v>1.953000727972921</v>
+        <v>0.3173626182955998</v>
       </c>
       <c r="E3" t="n">
-        <v>10.5388278281932</v>
+        <v>1.712559522081396</v>
       </c>
       <c r="F3" t="n">
-        <v>24.94609779058719</v>
+        <v>4.053740890970418</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>88.00305819009036</v>
+        <v>14.30049695588968</v>
       </c>
       <c r="D4" t="n">
-        <v>8.423019476068987</v>
+        <v>1.36874066486121</v>
       </c>
       <c r="E4" t="n">
-        <v>10.5388278281932</v>
+        <v>1.712559522081396</v>
       </c>
       <c r="F4" t="n">
-        <v>24.94609779058719</v>
+        <v>4.053740890970418</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>106.692161543631</v>
+        <v>17.33747625084003</v>
       </c>
       <c r="D5" t="n">
-        <v>8.732124598286489</v>
+        <v>1.418970247221555</v>
       </c>
       <c r="E5" t="n">
-        <v>10.5388278281932</v>
+        <v>1.712559522081396</v>
       </c>
       <c r="F5" t="n">
-        <v>24.94609779058719</v>
+        <v>4.053740890970418</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>71.62549552102679</v>
+        <v>11.63914302216685</v>
       </c>
       <c r="D6" t="n">
-        <v>67.83638374423501</v>
+        <v>11.02341235843819</v>
       </c>
       <c r="E6" t="n">
-        <v>10.5388278281932</v>
+        <v>1.712559522081396</v>
       </c>
       <c r="F6" t="n">
-        <v>24.94609779058719</v>
+        <v>4.053740890970418</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>96.41314822106798</v>
+        <v>15.66713658592355</v>
       </c>
       <c r="D7" t="n">
-        <v>32.55623392910471</v>
+        <v>5.290388013479516</v>
       </c>
       <c r="E7" t="n">
-        <v>10.5388278281932</v>
+        <v>1.712559522081396</v>
       </c>
       <c r="F7" t="n">
-        <v>24.94609779058719</v>
+        <v>4.053740890970418</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>91.36659940376963</v>
+        <v>14.84707240311256</v>
       </c>
       <c r="D8" t="n">
-        <v>61.78267882766278</v>
+        <v>10.0396853094952</v>
       </c>
       <c r="E8" t="n">
-        <v>10.5388278281932</v>
+        <v>1.712559522081396</v>
       </c>
       <c r="F8" t="n">
-        <v>24.94609779058719</v>
+        <v>4.053740890970418</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
